--- a/шаблон_задачи.xlsx
+++ b/шаблон_задачи.xlsx
@@ -255,6 +255,11 @@
         <t>Число - сотрудник узнаёт его, написав боту /start</t>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Не используется ботом, только чтобы не перепутать людей, пока не пришли реальные chat_id</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -548,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -608,6 +613,13 @@
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Жёлтые ячейки - заполняете вы. Серые - заполняет бот, трогать не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Столбец «Контакт» на листе «Сотрудники» - справочный, ботом не используется, нужен только чтобы не перепутать людей, пока не проставлены реальные Telegram Chat ID.</t>
         </is>
       </c>
     </row>
@@ -738,11 +750,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -756,25 +769,166 @@
           <t>Telegram Chat ID</t>
         </is>
       </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Контакт (ник/телефон) - для сверки</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Артем</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>111111111</v>
+          <t>Артур Верменич</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>0 67 488 17 40</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Марина</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>222222222</v>
+          <t>Вова Гордовой</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>@vutaliyzevsparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Денис Бодлев</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>@Bodleevv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Алина Балагур</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0 67 114 41 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Андрей Авраменко</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>@takbudetnevsegda</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Артем Деменников</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>@artem_zevsparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Володимир Биб</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>@volodymyr_zevsparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Марина Андріенко</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0 67 416 77 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Олександр Миклухо</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>@alexzevsparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Олександр Бодлєв</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>@alexandro_zevs_parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Святослав Чванов</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>@Zevspartssviat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Юлия Вагина</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0671389817</t>
+        </is>
       </c>
     </row>
   </sheetData>
